--- a/artfynd/A 4943-2022 artfynd.xlsx
+++ b/artfynd/A 4943-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4943-2022 artfynd.xlsx
+++ b/artfynd/A 4943-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130110395</v>
       </c>
       <c r="B3" t="n">
-        <v>92338</v>
+        <v>92340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4943-2022 artfynd.xlsx
+++ b/artfynd/A 4943-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130110395</v>
       </c>
       <c r="B3" t="n">
-        <v>92340</v>
+        <v>92427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4943-2022 artfynd.xlsx
+++ b/artfynd/A 4943-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130110395</v>
       </c>
       <c r="B3" t="n">
-        <v>92427</v>
+        <v>92430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4943-2022 artfynd.xlsx
+++ b/artfynd/A 4943-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130110395</v>
       </c>
       <c r="B3" t="n">
-        <v>92430</v>
+        <v>92456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4943-2022 artfynd.xlsx
+++ b/artfynd/A 4943-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>176720</v>
+        <v>133827907</v>
       </c>
       <c r="B2" t="n">
-        <v>90170</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>517</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinntagging</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dentipellis fragilis</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers. : Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Engelbrektsholmen, Nrk</t>
+          <t>Engelbrektsholmen, Engelbrektsholmen, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532469.1752209929</v>
+        <v>532419</v>
       </c>
       <c r="R2" t="n">
-        <v>6571202.37563119</v>
+        <v>6571091</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-01-23</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-01-23</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,69 +775,64 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>på gren av hassel eller lind</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Magnus Friberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Magnus Friberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130110395</v>
+        <v>176720</v>
       </c>
       <c r="B3" t="n">
-        <v>92456</v>
+        <v>92729</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1527</v>
+        <v>517</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Prakttagging</t>
+          <t>Skinntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Steccherinum robustius</t>
+          <t>Dentipellis fragilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+          <t>(Pers.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Engelbrektsholmen, Engelbrektsholmen, Nrk</t>
+          <t>Engelbrektsholmen, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532467</v>
+        <v>532469</v>
       </c>
       <c r="R3" t="n">
-        <v>6571184</v>
+        <v>6571202</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:54</t>
+          <t>2008-01-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:54</t>
+          <t>2008-01-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,19 +872,352 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>på gren av hassel eller lind</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Herbert Kaufmann</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Herbert Kaufmann</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130110395</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92613</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1527</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Prakttagging</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Steccherinum robustius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(J.Erikss. &amp; S.Lundell) J.Erikss.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Engelbrektsholmen, Engelbrektsholmen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>532467</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6571184</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Mellösa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Magnus Friberg</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Magnus Friberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123875695</v>
+      </c>
+      <c r="B5" t="n">
+        <v>107609</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Engelbrektsholmen, Engelbrektsholmen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>532469</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6571049</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Mellösa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100148992</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Engelbrektsholmen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>532495</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6571069</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Mellösa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Friberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4943-2022 artfynd.xlsx
+++ b/artfynd/A 4943-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133827907</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/176720</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130110395</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123875695</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,8 +1243,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100148992</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>